--- a/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_3_flies_sort_enu_kad.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_3_flies_sort_enu_kad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B798FE-5FE5-4619-9649-44610EB510AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9206BF9-18BF-44AA-A7A4-A218A6211E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="313">
   <si>
     <t>type</t>
   </si>
@@ -354,12 +354,6 @@
     <t>community = ${r_community}</t>
   </si>
   <si>
-    <t>ng_oncho_2505_3_flies_sort_enu_kad</t>
-  </si>
-  <si>
-    <t>(Enugu Kaduna) 3. Blackfly Sorting Modules V4</t>
-  </si>
-  <si>
     <t>ENUGU</t>
   </si>
   <si>
@@ -970,6 +964,18 @@
   </si>
   <si>
     <t>KAD_JEM_M_001</t>
+  </si>
+  <si>
+    <t>UGWOGO</t>
+  </si>
+  <si>
+    <t>ENU_ENE_M_096</t>
+  </si>
+  <si>
+    <t>(Enugu Kaduna) 3. Blackfly Sorting Modules V2</t>
+  </si>
+  <si>
+    <t>ng_oncho_2505_3_flies_sort_enu_kad_v2</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1188,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2323,10 +2339,10 @@
         <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2334,27 +2350,24 @@
         <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
         <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,13 +2375,13 @@
         <v>93</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2376,13 +2389,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2390,13 +2403,13 @@
         <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2404,125 +2417,128 @@
         <v>93</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D30" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="D33" t="s">
-        <v>108</v>
-      </c>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="23"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2530,13 +2546,13 @@
         <v>94</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2544,13 +2560,13 @@
         <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2558,13 +2574,13 @@
         <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2572,13 +2588,13 @@
         <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
       <c r="E39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2586,13 +2602,13 @@
         <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2600,13 +2616,13 @@
         <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2614,1248 +2630,1245 @@
         <v>94</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E52" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E59" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E64" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E44" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E54" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E55" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B56" s="1" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E71" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E72" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E74" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E75" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E78" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E81" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E83" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E84" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E86" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E87" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E88" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E89" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E90" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E91" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E92" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E94" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E95" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>94</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E98" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>94</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E99" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>94</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E100" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E101" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E102" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>94</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E103" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>94</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E104" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>94</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>94</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E106" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>94</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>94</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E108" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>94</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E109" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>94</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E110" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>94</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E111" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>94</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E112" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>94</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E113" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>94</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E114" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>94</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E115" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>94</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>94</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E118" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>94</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>94</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>94</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E56" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E58" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E59" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E60" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E61" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E62" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E63" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E64" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E65" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E66" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E67" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E68" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E69" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E70" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E72" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E73" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E75" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E76" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E77" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E79" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E80" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E81" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E83" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E84" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E85" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E86" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E87" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E88" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E90" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E91" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E92" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E93" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="E121" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E95" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E122" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E96" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>94</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E123" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E97" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E98" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E99" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E100" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>94</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E124" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E101" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>94</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E125" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E102" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>94</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E126" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E103" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>94</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E127" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E104" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>94</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E128" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E105" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>94</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E129" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E106" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>94</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E130" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E107" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E108" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E109" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E110" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E111" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E112" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E113" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E114" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E115" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E116" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E117" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E118" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E120" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E121" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E122" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E123" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E124" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E125" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E126" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E127" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E128" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E129" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="23"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F131" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,13 +3876,13 @@
         <v>69</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="F132" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3877,13 +3890,13 @@
         <v>69</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="F133" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3891,13 +3904,13 @@
         <v>69</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="F134" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3905,13 +3918,13 @@
         <v>69</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="F135" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3919,13 +3932,13 @@
         <v>69</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="F136" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,13 +3946,13 @@
         <v>69</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="F137" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3947,13 +3960,13 @@
         <v>69</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="F138" t="s">
-        <v>141</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -3961,13 +3974,13 @@
         <v>69</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F139" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -3975,13 +3988,13 @@
         <v>69</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F140" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -3989,13 +4002,13 @@
         <v>69</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F141" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,13 +4016,13 @@
         <v>69</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F142" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4017,13 +4030,13 @@
         <v>69</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="F143" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,13 +4044,13 @@
         <v>69</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="F144" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,13 +4058,13 @@
         <v>69</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="F145" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4059,13 +4072,13 @@
         <v>69</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="F146" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4073,13 +4086,13 @@
         <v>69</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="F147" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4087,13 +4100,13 @@
         <v>69</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="F148" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,13 +4114,13 @@
         <v>69</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="F149" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,13 +4128,13 @@
         <v>69</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="F150" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,13 +4142,13 @@
         <v>69</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="F151" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4143,13 +4156,13 @@
         <v>69</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="F152" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,13 +4170,13 @@
         <v>69</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F153" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4171,13 +4184,13 @@
         <v>69</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="F154" t="s">
-        <v>198</v>
+        <v>137</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4185,13 +4198,13 @@
         <v>69</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F155" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,13 +4212,13 @@
         <v>69</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="F156" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,13 +4226,13 @@
         <v>69</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="F157" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4227,13 +4240,13 @@
         <v>69</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="F158" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4241,13 +4254,13 @@
         <v>69</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F159" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,13 +4268,13 @@
         <v>69</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F160" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4269,13 +4282,13 @@
         <v>69</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="F161" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4283,13 +4296,13 @@
         <v>69</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="F162" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,13 +4310,13 @@
         <v>69</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="F163" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,13 +4324,13 @@
         <v>69</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="F164" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4325,13 +4338,13 @@
         <v>69</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="F165" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,13 +4352,13 @@
         <v>69</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,13 +4366,13 @@
         <v>69</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F167" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4367,13 +4380,13 @@
         <v>69</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="F168" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4381,13 +4394,13 @@
         <v>69</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="F169" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,13 +4408,13 @@
         <v>69</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F170" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,13 +4422,13 @@
         <v>69</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="F171" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4423,13 +4436,13 @@
         <v>69</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="F172" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4437,13 +4450,13 @@
         <v>69</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="F173" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4451,13 +4464,13 @@
         <v>69</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="F174" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4465,13 +4478,13 @@
         <v>69</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="F175" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,13 +4492,13 @@
         <v>69</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="F176" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,13 +4506,13 @@
         <v>69</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F177" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -4507,13 +4520,13 @@
         <v>69</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="F178" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -4521,13 +4534,13 @@
         <v>69</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="F179" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,13 +4548,13 @@
         <v>69</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F180" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -4549,13 +4562,13 @@
         <v>69</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F181" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -4563,13 +4576,13 @@
         <v>69</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F182" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4577,13 +4590,13 @@
         <v>69</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="F183" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,13 +4604,13 @@
         <v>69</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F184" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,13 +4618,13 @@
         <v>69</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F185" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,13 +4632,13 @@
         <v>69</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="F186" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,13 +4646,13 @@
         <v>69</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F187" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -4647,13 +4660,13 @@
         <v>69</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="F188" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -4661,13 +4674,13 @@
         <v>69</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="F189" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,13 +4688,13 @@
         <v>69</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F190" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -4689,13 +4702,13 @@
         <v>69</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="F191" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4703,13 +4716,13 @@
         <v>69</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F192" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -4717,13 +4730,13 @@
         <v>69</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F193" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -4731,13 +4744,13 @@
         <v>69</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="F194" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -4745,13 +4758,13 @@
         <v>69</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F195" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,13 +4772,13 @@
         <v>69</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F196" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,13 +4786,13 @@
         <v>69</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F197" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -4787,13 +4800,13 @@
         <v>69</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="F198" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,13 +4814,13 @@
         <v>69</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F199" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,13 +4828,13 @@
         <v>69</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="F200" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -4829,13 +4842,13 @@
         <v>69</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F201" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -4843,13 +4856,13 @@
         <v>69</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F202" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -4857,13 +4870,13 @@
         <v>69</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="F203" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -4871,13 +4884,13 @@
         <v>69</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F204" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -4885,13 +4898,13 @@
         <v>69</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F205" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,13 +4912,13 @@
         <v>69</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="F206" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,13 +4926,13 @@
         <v>69</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="F207" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -4927,13 +4940,13 @@
         <v>69</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="F208" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -4941,13 +4954,13 @@
         <v>69</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F209" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,13 +4968,13 @@
         <v>69</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="F210" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -4969,13 +4982,13 @@
         <v>69</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="F211" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -4983,13 +4996,13 @@
         <v>69</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="F212" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -4997,13 +5010,13 @@
         <v>69</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="F213" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5011,13 +5024,13 @@
         <v>69</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="F214" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5025,13 +5038,13 @@
         <v>69</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="F215" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,13 +5052,13 @@
         <v>69</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="F216" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5053,13 +5066,13 @@
         <v>69</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="F217" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5067,13 +5080,13 @@
         <v>69</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F218" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -5081,13 +5094,13 @@
         <v>69</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F219" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,13 +5108,13 @@
         <v>69</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F220" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -5109,13 +5122,13 @@
         <v>69</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F221" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -5123,13 +5136,13 @@
         <v>69</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F222" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5137,13 +5150,13 @@
         <v>69</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F223" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -5151,13 +5164,13 @@
         <v>69</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F224" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -5165,13 +5178,13 @@
         <v>69</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="F225" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -5179,20 +5192,42 @@
         <v>69</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="F226" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="23"/>
+      <c r="A227" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F227" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="23"/>
+      <c r="A228" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F228" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="23"/>
@@ -5465,7 +5500,7 @@
       <c r="A318" s="23"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C44">
+  <conditionalFormatting sqref="C132">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5497,10 +5532,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>106</v>
+        <v>311</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>105</v>
+        <v>312</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>19</v>
